--- a/config/wallets.example.xlsx
+++ b/config/wallets.example.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="wallets" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,28 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <color rgb="00808080"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +61,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,25 +433,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="74" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>приватный ключ (0x...)</t>
+          <t>приватный ключ кошелька (столбец A)</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>адрес депозита ETH на Bitget (0x...)</t>
+          <t>адрес депозита ETH на Bitget (столбец B)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
-          <t># одна строка = один аккаунт; строки с # игнорируются</t>
+          <t># 0x1111111111111111111111111111111111111111111111111111111111111111</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t># 0x2222222222222222222222222222222222222222</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t># ↑ пример формата (строки с # пропускаются). Свои кошельки впиши ниже БЕЗ #, по одному на строку.</t>
         </is>
       </c>
     </row>
